--- a/arenes.xlsx
+++ b/arenes.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3840" yWindow="3360" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="arenes" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,12 +17,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -46,8 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -614,6 +624,171 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test 2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ville 2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dresseur </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>foret</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test 3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ville 3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dressur</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ville 4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dresseur</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>cyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test 5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ville</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dresur</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>tt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tt</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>tt</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tt</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>grey</t>
         </is>
       </c>
     </row>
@@ -629,32 +804,322 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.6" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>arene_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pv</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>attaque</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>niveau</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_bonus</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>double_vie</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pokemon1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pokemon2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pokemon3</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pokemon4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pokemon5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pokemon test </t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pokemon test 2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>500</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pp</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>500</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/arenes.xlsx
+++ b/arenes.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="arenes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="pokemons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pokemons" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="arenes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -17,19 +17,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,8 +445,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="12.6640625" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -471,27 +464,37 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ville</t>
+          <t>arene_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>dresseur</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>pv</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>attaque</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>niveau</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_bonus</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>double_vies</t>
         </is>
       </c>
     </row>
@@ -501,31 +504,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arene feu</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Motorby</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Kabu</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Feu</t>
-        </is>
+          <t>pokemon  1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -534,31 +535,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arene eau</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Papeloa</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Amana</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Eau</t>
-        </is>
+          <t>pokemon  2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>cyan</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -567,31 +566,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arene foret</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cuencia</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Colza</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Foret</t>
-        </is>
+          <t>pokemon  3</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -600,31 +597,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ville</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>dresseur</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
+          <t>pokemon  4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>yellow</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -633,31 +628,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>test 2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ville 2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dresseur </t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>foret</t>
-        </is>
+          <t>pokemon  5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>cyan</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -666,31 +659,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>test 3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ville 3</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>dressur</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
+          <t>pokemon  6</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -699,102 +690,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>test4</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ville 4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>dresseur</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
+          <t>pokemon  7</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>cyan</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>test 5</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ville</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>dresur</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>100</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>grey</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>tt</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>tt</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>tt</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>tt</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>100</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>grey</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -804,10 +726,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1">
+    <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
@@ -820,37 +742,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>arene_id</t>
+          <t>ville</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>dressur</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>pv</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>attaque</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>niveau</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>points_bonus</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>double_vie</t>
+          <t>color</t>
         </is>
       </c>
     </row>
@@ -860,30 +772,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pokemon1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" t="n">
-        <v>100</v>
+          <t>arene feu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ville 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dresseur 1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>type 1</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>True</t>
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -893,30 +805,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pokemon2</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>100</v>
+          <t>arene eau</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ville 2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dresseur 2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>type 2</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>True</t>
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
     </row>
@@ -926,200 +838,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pokemon3</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" t="n">
-        <v>100</v>
+          <t>arene foret</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ville 3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dresseur 3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>type 3</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>pokemon4</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>pokemon5</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>100</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pokemon test </t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>500</v>
-      </c>
-      <c r="F7" t="n">
-        <v>100</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>pokemon test 2</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>500</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>pp</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>500</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>oui</t>
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/arenes.xlsx
+++ b/arenes.xlsx
@@ -514,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -573,16 +573,16 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>

--- a/arenes.xlsx
+++ b/arenes.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4848" yWindow="3360" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="pokemons" sheetId="1" state="visible" r:id="rId1"/>
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.6640625" customWidth="1" min="2" max="2"/>
@@ -511,16 +512,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -542,16 +543,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -573,16 +574,16 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -607,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -714,6 +715,9 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="14">
+      <c r="E14" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
